--- a/boda/seating-plan/invitados.xlsx
+++ b/boda/seating-plan/invitados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mtorrecillas\Documents\GitHub\web\boda\seating-plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{522D4577-8659-4976-B897-AADE55CCFEA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDE727C5-F4F6-4D5B-AB9B-A04CDE6563BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{DED33C3B-955C-4A32-AC59-5EB52B2DA8D6}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="114">
   <si>
     <t>Espe</t>
   </si>
@@ -378,6 +378,12 @@
   </si>
   <si>
     <t>Padres Manuel</t>
+  </si>
+  <si>
+    <t>Helena</t>
+  </si>
+  <si>
+    <t>Carolina</t>
   </si>
 </sst>
 </file>
@@ -474,8 +480,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -811,7 +817,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DA8DADE-4765-4C42-9EB0-CA962E802060}">
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.26953125" bestFit="1" customWidth="1"/>
@@ -2963,9 +2969,49 @@
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="G94">
-        <f>SUM(G2:G93)</f>
-        <v>189</v>
+      <c r="A94" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G94" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A95" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G95" s="2">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
